--- a/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/二次圈矿成果_3970_1011/3970平台 1011炮孔数据报告.xlsx
+++ b/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/二次圈矿成果_3970_1011/3970平台 1011炮孔数据报告.xlsx
@@ -35,22 +35,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -79,21 +69,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -534,22 +522,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="n">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n">
         <v>644.721</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="5" t="n">
         <v>1732.03</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.135</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="5" t="n">
         <v>19.659</v>
       </c>
     </row>
@@ -598,42 +586,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="n">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n">
         <v>13678.123</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="5" t="n">
         <v>36670.209</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="5" t="n">
         <v>0.542</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="5" t="n">
         <v>198.85</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="n">
         <v>14322.844</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="7" t="n">
         <v>38402.24</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="7" t="n">
         <v>0.569</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="7" t="n">
         <v>218.509</v>
       </c>
     </row>
@@ -646,7 +634,7 @@
       <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>炮孔品位统计（孔数）</t>
         </is>

--- a/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/二次圈矿成果_3970_1011/3970平台 1011炮孔数据报告.xlsx
+++ b/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/二次圈矿成果_3970_1011/3970平台 1011炮孔数据报告.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -509,16 +509,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>644.721</v>
+        <v>513.7380000000001</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1732.03</v>
+        <v>1386.732</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>1.135</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>19.659</v>
+        <v>15.739</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="5" t="n">
-        <v>644.721</v>
+        <v>513.7380000000001</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1732.03</v>
+        <v>1386.732</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>1.135</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>19.659</v>
+        <v>15.739</v>
       </c>
     </row>
     <row r="5">
@@ -551,82 +551,72 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>12526.004</v>
+        <v>8754.351000000001</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>33580.17</v>
+        <v>23558.98</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.52</v>
+        <v>0.651</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>174.473</v>
+        <v>153.413</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="5" t="n">
-        <v>1152.119</v>
+        <v>8754.351000000001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3090.039</v>
+        <v>23558.98</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.789</v>
+        <v>0.651</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24.378</v>
+        <v>153.413</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n">
-        <v>13678.123</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>36670.209</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>198.85</v>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>9268.089</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>24945.712</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>169.153</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>14322.844</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>38402.24</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>218.509</v>
-      </c>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>炮孔品位统计（孔数）</t>
+        </is>
+      </c>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -634,66 +624,54 @@
       <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>炮孔品位统计（孔数）</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>≥3</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>1.5-3</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>1-1.5</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>≥3</t>
+          <t>0.5-1</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>1.5-3</t>
+          <t>&lt;0.5</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1-1.5</t>
+          <t>合计孔数</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>0.5-1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>&lt;0.5</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>合计孔数</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
         <v>66</v>
       </c>
     </row>

--- a/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/二次圈矿成果_3970_1011/3970平台 1011炮孔数据报告.xlsx
+++ b/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/二次圈矿成果_3970_1011/3970平台 1011炮孔数据报告.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -509,169 +509,213 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>513.7380000000001</v>
+        <v>658.759</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1386.732</v>
+        <v>1768.192</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1.135</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>15.739</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>小计</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
+          <t>1.000-1.500</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="C4" s="5" t="n">
-        <v>513.7380000000001</v>
+        <v>554.048</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1386.732</v>
+        <v>1494.476</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>1.135</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>15.739</v>
+        <v>16.962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
       <c r="C5" s="5" t="n">
-        <v>8754.351000000001</v>
+        <v>1212.807</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>23558.98</v>
+        <v>3262.669</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.651</v>
+        <v>0.963</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>153.413</v>
+        <v>31.412</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>0.500-1.000</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6196.65</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16680.951</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>104.202</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>0.500-1.000</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1858.632</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5002.093</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>33.014</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n">
-        <v>8754.351000000001</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>23558.98</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>153.413</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>9268.089</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>24945.712</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>169.153</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>8055.282</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>21683.043</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>137.216</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>9268.089</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>24945.712</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>168.628</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>炮孔品位统计（孔数）</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>≥3</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>1.5-3</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1-1.5</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>0.5-1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>&lt;0.5</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D13" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>合计孔数</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>66</v>
       </c>
     </row>
